--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1431,6 +1431,234 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123772955</v>
+      </c>
+      <c r="B8" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>340</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chimaphila umbellata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Horna, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>455580</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6201987</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 200 st i 2025-03-17  avverkningsanmäld skog !</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123773198</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97350</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Horna, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>455645</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6201865</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ca 15 kvm i kanten av 2024-03-12 avverkningsanmäld skog</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1436,7 +1436,7 @@
         <v>123772955</v>
       </c>
       <c r="B8" t="n">
-        <v>105463</v>
+        <v>105479</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>123773198</v>
       </c>
       <c r="B9" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1311,14 +1311,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113740724</v>
+        <v>123772955</v>
       </c>
       <c r="B7" t="n">
-        <v>104698</v>
+        <v>105481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1346,28 +1346,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Horna. Oredslund, 2,0 km SSV, Sk</t>
+          <t>Horna, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455585</v>
+        <v>455580</v>
       </c>
       <c r="R7" t="n">
-        <v>6201856</v>
+        <v>6201987</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,19 +1387,19 @@
           <t>Rinkaby</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>M-Kri-0658</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca 200 st i 2025-03-17  avverkningsanmäld skog !</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,26 +1415,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Hans Ingvarsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123772955</v>
+        <v>123773198</v>
       </c>
       <c r="B8" t="n">
-        <v>105479</v>
+        <v>97369</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1445,32 +1439,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>340</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1481,13 +1471,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455580</v>
+        <v>455645</v>
       </c>
       <c r="R8" t="n">
-        <v>6201987</v>
+        <v>6201865</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1521,7 +1511,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca 200 st i 2025-03-17  avverkningsanmäld skog !</t>
+          <t>ca 15 kvm i kanten av 2024-03-12 avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1546,118 +1536,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>123773198</v>
-      </c>
-      <c r="B9" t="n">
-        <v>97367</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Horna, Sk</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>455645</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6201865</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Kristianstad</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Rinkaby</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ca 15 kvm i kanten av 2024-03-12 avverkningsanmäld skog</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Hans Ingvarsson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Hans Ingvarsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123772955</v>
+        <v>123773198</v>
       </c>
       <c r="B7" t="n">
-        <v>105481</v>
+        <v>96957</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,32 +1323,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>340</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1359,13 +1355,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455580</v>
+        <v>455645</v>
       </c>
       <c r="R7" t="n">
-        <v>6201987</v>
+        <v>6201865</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1399,7 +1395,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 200 st i 2025-03-17  avverkningsanmäld skog !</t>
+          <t>ca 15 kvm i kanten av 2024-03-12 avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,10 +1423,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123773198</v>
+        <v>123772955</v>
       </c>
       <c r="B8" t="n">
-        <v>97369</v>
+        <v>105056</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1439,28 +1435,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>340</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455645</v>
+        <v>455580</v>
       </c>
       <c r="R8" t="n">
-        <v>6201865</v>
+        <v>6201987</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ca 15 kvm i kanten av 2024-03-12 avverkningsanmäld skog</t>
+          <t>Ca 200 st i 2025-03-17  avverkningsanmäld skog !</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123773198</v>
+        <v>123772955</v>
       </c>
       <c r="B7" t="n">
-        <v>96957</v>
+        <v>105056</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,28 +1323,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>340</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1355,13 +1359,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455645</v>
+        <v>455580</v>
       </c>
       <c r="R7" t="n">
-        <v>6201865</v>
+        <v>6201987</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1395,7 +1399,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ca 15 kvm i kanten av 2024-03-12 avverkningsanmäld skog</t>
+          <t>Ca 200 st i 2025-03-17  avverkningsanmäld skog !</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,10 +1427,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123772955</v>
+        <v>123773198</v>
       </c>
       <c r="B8" t="n">
-        <v>105056</v>
+        <v>96957</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1435,32 +1439,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>340</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455580</v>
+        <v>455645</v>
       </c>
       <c r="R8" t="n">
-        <v>6201987</v>
+        <v>6201865</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca 200 st i 2025-03-17  avverkningsanmäld skog !</t>
+          <t>ca 15 kvm i kanten av 2024-03-12 avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123772955</v>
+        <v>123773198</v>
       </c>
       <c r="B7" t="n">
-        <v>105056</v>
+        <v>96957</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,32 +1323,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>340</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1359,13 +1355,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455580</v>
+        <v>455645</v>
       </c>
       <c r="R7" t="n">
-        <v>6201987</v>
+        <v>6201865</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1399,7 +1395,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 200 st i 2025-03-17  avverkningsanmäld skog !</t>
+          <t>ca 15 kvm i kanten av 2024-03-12 avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,10 +1423,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123773198</v>
+        <v>123772955</v>
       </c>
       <c r="B8" t="n">
-        <v>96957</v>
+        <v>105056</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1439,28 +1435,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>340</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455645</v>
+        <v>455580</v>
       </c>
       <c r="R8" t="n">
-        <v>6201865</v>
+        <v>6201987</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ca 15 kvm i kanten av 2024-03-12 avverkningsanmäld skog</t>
+          <t>Ca 200 st i 2025-03-17  avverkningsanmäld skog !</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455707.7848457819</v>
+        <v>455708</v>
       </c>
       <c r="R2" t="n">
-        <v>6201940.635711916</v>
+        <v>6201941</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1993-06-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1993-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>103226</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455707.7848457819</v>
+        <v>455708</v>
       </c>
       <c r="R3" t="n">
-        <v>6201940.635711916</v>
+        <v>6201941</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +859,9 @@
           <t>1993-06-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1993-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -940,12 +910,7 @@
         <v>63715097</v>
       </c>
       <c r="B4" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455707.7848457819</v>
+        <v>455708</v>
       </c>
       <c r="R4" t="n">
-        <v>6201940.635711916</v>
+        <v>6201941</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1010,19 +975,9 @@
           <t>1993-06-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1993-06-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>105591</v>
+        <v>105603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63715097</v>
       </c>
       <c r="B4" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>105603</v>
+        <v>105612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>105612</v>
+        <v>105615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63715097</v>
       </c>
       <c r="B4" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>105615</v>
+        <v>105643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63715097</v>
       </c>
       <c r="B4" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>105643</v>
+        <v>105649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63715097</v>
       </c>
       <c r="B4" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>105649</v>
+        <v>105656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63715097</v>
       </c>
       <c r="B4" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>105656</v>
+        <v>105660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63715097</v>
       </c>
       <c r="B4" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>105660</v>
+        <v>105667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63715097</v>
       </c>
       <c r="B4" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>105670</v>
+        <v>105675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63715097</v>
       </c>
       <c r="B4" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>105675</v>
+        <v>105683</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63715097</v>
       </c>
       <c r="B4" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63715096</v>
       </c>
       <c r="B2" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63715094</v>
       </c>
       <c r="B3" t="n">
-        <v>105683</v>
+        <v>105693</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63715097</v>
       </c>
       <c r="B4" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1139,12 +1139,7 @@
         <v>76327464</v>
       </c>
       <c r="B6" t="n">
-        <v>103226</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>105751</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455584.6470222725</v>
+        <v>455585</v>
       </c>
       <c r="R6" t="n">
-        <v>6201856.267862211</v>
+        <v>6201856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,19 +1218,9 @@
           <t>2019-03-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-03-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>76327464</v>
       </c>
       <c r="B6" t="n">
-        <v>105751</v>
+        <v>105754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>76327464</v>
       </c>
       <c r="B6" t="n">
-        <v>105754</v>
+        <v>105783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>76327464</v>
       </c>
       <c r="B6" t="n">
-        <v>105783</v>
+        <v>105795</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>76327464</v>
       </c>
       <c r="B6" t="n">
-        <v>105795</v>
+        <v>105796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>76327464</v>
       </c>
       <c r="B6" t="n">
-        <v>105796</v>
+        <v>105801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>76327464</v>
       </c>
       <c r="B6" t="n">
-        <v>105801</v>
+        <v>105805</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>76327464</v>
       </c>
       <c r="B6" t="n">
-        <v>105805</v>
+        <v>105807</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12799-2025 artfynd.xlsx
+++ b/artfynd/A 12799-2025 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>76327464</v>
       </c>
       <c r="B6" t="n">
-        <v>105807</v>
+        <v>105817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
